--- a/Report Test subject/results/OSMS-Final-Test-Results.xlsx
+++ b/Report Test subject/results/OSMS-Final-Test-Results.xlsx
@@ -8,35 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Online-Sales-Management-System\Report Test subject\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85F0F9BA-7782-4035-8548-523A1E013582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{141229AF-2FE5-48BA-8425-47DF1F3DD8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE3B982E-0965-480C-B85B-F51CE8B5380D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21F68D93-0B7E-4AEC-BFE9-49B639319227}"/>
   </bookViews>
   <sheets>
-    <sheet name="FinalResults" sheetId="1" r:id="rId1"/>
+    <sheet name="OSMS-Final-Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="305">
   <si>
     <t>Execution Date</t>
   </si>
@@ -116,246 +100,237 @@
     <t>JSON response contains page, pageSize, totalItems, totalPages, and items array; items array contains active products with fields such as id, sku, name, categoryName, brandName, salePrice, stockOnHand.</t>
   </si>
   <si>
+    <t>Request returned the expected HTTP status and passed all Newman assertions in the full collection run on 2026-04-06.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>N/A - text runner artifact used</t>
+  </si>
+  <si>
+    <t>results/automation-api/newman-full-run.txt</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Covered by the full Newman collection run saved as text and JUnit artifacts.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-002</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint supports search by SKU or product name</t>
+  </si>
+  <si>
+    <t>JSON response returns matching items only; at least one returned item contains the searched SKU or product name.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-003</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint filters by valid categoryId</t>
+  </si>
+  <si>
+    <t>All returned items have categoryId=30012 or the items array is empty without error; response structure remains valid.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-004</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint filters by valid brandId</t>
+  </si>
+  <si>
+    <t>All returned items have brandId=30039 or the items array is empty without error; response structure remains valid.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-005</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint supports valid price range and sort parameters</t>
+  </si>
+  <si>
+    <t>Response is valid; each returned item salePrice stays within requested range; items are sorted in ascending price order.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-006</t>
+  </si>
+  <si>
+    <t>SCN-API-003</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects page less than 1</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=page, and message states page must be greater than 0.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-007</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects pageSize less than 1</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=pageSize, and message states page size must be between 1 and 100.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-008</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects pageSize greater than 100</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-009</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects negative minPrice</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=minPrice, and message states minimum price cannot be negative.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-010</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects negative maxPrice</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=maxPrice, and message states maximum price cannot be negative.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-011</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects minPrice greater than maxPrice</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=priceRange, and message states minimum price cannot be greater than maximum price.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-012</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects unsupported sort option</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=sort, and message states sort must be one of default, price_asc, price_desc, newest.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-013</t>
+  </si>
+  <si>
+    <t>Catalog products endpoint rejects page value that exceeds total pages</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=page, and message states the requested page exceeds total pages.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-014</t>
+  </si>
+  <si>
+    <t>SCN-API-004</t>
+  </si>
+  <si>
+    <t>Catalog product detail endpoint returns expected payload for valid active product</t>
+  </si>
+  <si>
+    <t>JSON response contains id=30073 and expected detail fields including sku, name, categoryName, brandName, unitName, costPrice, salePrice, stockOnHand, reorderLevel, isTrending, and imagePath.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-015</t>
+  </si>
+  <si>
+    <t>SCN-API-005</t>
+  </si>
+  <si>
+    <t>Catalog product detail endpoint rejects id less than or equal to zero</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=validation_error, target=id, and message states id must be greater than 0.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-016</t>
+  </si>
+  <si>
+    <t>Catalog product detail endpoint returns not_found for unknown active product id</t>
+  </si>
+  <si>
+    <t>JSON error response contains code=not_found, target=id, and message states product not found.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-017</t>
+  </si>
+  <si>
+    <t>SCN-API-006</t>
+  </si>
+  <si>
+    <t>Trending endpoint returns active trending categories and products</t>
+  </si>
+  <si>
+    <t>JSON response contains categories array and products array; each entry uses the expected schema for lookup or product items.</t>
+  </si>
+  <si>
+    <t>TC-API-CAT-018</t>
+  </si>
+  <si>
+    <t>Filters endpoint returns active categories and brands with product counts</t>
+  </si>
+  <si>
+    <t>JSON response contains categories array and brands array; each entry includes id, name, and productCount.</t>
+  </si>
+  <si>
+    <t>TC-API-HLT-001</t>
+  </si>
+  <si>
+    <t>SCN-API-001</t>
+  </si>
+  <si>
+    <t>Health API</t>
+  </si>
+  <si>
+    <t>Health endpoint returns service availability metadata</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>JSON response contains non-empty fields for status, service, serverTimeUtc, and version; status value is ok.</t>
+  </si>
+  <si>
+    <t>Health endpoint returned 200 OK and all Newman assertions for status, service, serverTimeUtc, and version passed in the full collection rerun.</t>
+  </si>
+  <si>
+    <t>Confirmed again in the full Newman collection run on 2026-04-06.</t>
+  </si>
+  <si>
+    <t>TC-UI-ADM-001</t>
+  </si>
+  <si>
+    <t>SCN-GOV-004</t>
+  </si>
+  <si>
+    <t>Admin Users</t>
+  </si>
+  <si>
+    <t>Admin UI</t>
+  </si>
+  <si>
+    <t>Create a new admin user with valid group assignment</t>
+  </si>
+  <si>
+    <t>Hoang Van Thien</t>
+  </si>
+  <si>
+    <t>System creates the new admin account successfully; success toast appears; the new account is visible in the admin user list.</t>
+  </si>
+  <si>
     <t>PENDING REAL EXECUTION</t>
   </si>
   <si>
     <t>Not Run</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Pending full catalog run</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-002</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint supports search by SKU or product name</t>
-  </si>
-  <si>
-    <t>JSON response returns matching items only; at least one returned item contains the searched SKU or product name.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-003</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint filters by valid categoryId</t>
-  </si>
-  <si>
-    <t>All returned items have categoryId=30012 or the items array is empty without error; response structure remains valid.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-004</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint filters by valid brandId</t>
-  </si>
-  <si>
-    <t>All returned items have brandId=30039 or the items array is empty without error; response structure remains valid.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-005</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint supports valid price range and sort parameters</t>
-  </si>
-  <si>
-    <t>Response is valid; each returned item salePrice stays within requested range; items are sorted in ascending price order.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-006</t>
-  </si>
-  <si>
-    <t>SCN-API-003</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects page less than 1</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=page, and message states page must be greater than 0.</t>
-  </si>
-  <si>
-    <t>Pending validation run</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-007</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects pageSize less than 1</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=pageSize, and message states page size must be between 1 and 100.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-008</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects pageSize greater than 100</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-009</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects negative minPrice</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=minPrice, and message states minimum price cannot be negative.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-010</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects negative maxPrice</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=maxPrice, and message states maximum price cannot be negative.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-011</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects minPrice greater than maxPrice</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=priceRange, and message states minimum price cannot be greater than maximum price.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-012</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects unsupported sort option</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=sort, and message states sort must be one of default, price_asc, price_desc, newest.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-013</t>
-  </si>
-  <si>
-    <t>Catalog products endpoint rejects page value that exceeds total pages</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=page, and message states the requested page exceeds total pages.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-014</t>
-  </si>
-  <si>
-    <t>SCN-API-004</t>
-  </si>
-  <si>
-    <t>Catalog product detail endpoint returns expected payload for valid active product</t>
-  </si>
-  <si>
-    <t>JSON response contains id=30073 and expected detail fields including sku, name, categoryName, brandName, unitName, costPrice, salePrice, stockOnHand, reorderLevel, isTrending, and imagePath.</t>
-  </si>
-  <si>
-    <t>Pending detail run</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-015</t>
-  </si>
-  <si>
-    <t>SCN-API-005</t>
-  </si>
-  <si>
-    <t>Catalog product detail endpoint rejects id less than or equal to zero</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=validation_error, target=id, and message states id must be greater than 0.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-016</t>
-  </si>
-  <si>
-    <t>Catalog product detail endpoint returns not_found for unknown active product id</t>
-  </si>
-  <si>
-    <t>JSON error response contains code=not_found, target=id, and message states product not found.</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-017</t>
-  </si>
-  <si>
-    <t>SCN-API-006</t>
-  </si>
-  <si>
-    <t>Trending endpoint returns active trending categories and products</t>
-  </si>
-  <si>
-    <t>JSON response contains categories array and products array; each entry uses the expected schema for lookup or product items.</t>
-  </si>
-  <si>
-    <t>Pending trending run</t>
-  </si>
-  <si>
-    <t>TC-API-CAT-018</t>
-  </si>
-  <si>
-    <t>Filters endpoint returns active categories and brands with product counts</t>
-  </si>
-  <si>
-    <t>JSON response contains categories array and brands array; each entry includes id, name, and productCount.</t>
-  </si>
-  <si>
-    <t>Pending filters run</t>
-  </si>
-  <si>
-    <t>TC-API-HLT-001</t>
-  </si>
-  <si>
-    <t>SCN-API-001</t>
-  </si>
-  <si>
-    <t>Health API</t>
-  </si>
-  <si>
-    <t>Health endpoint returns service availability metadata</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>JSON response contains non-empty fields for status, service, serverTimeUtc, and version; status value is ok.</t>
-  </si>
-  <si>
-    <t>Returned 200 OK and passed assertions for status service serverTimeUtc and version fields</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>N/A - text runner artifact used</t>
-  </si>
-  <si>
-    <t>results/automation-api/newman-health-smoke.txt</t>
-  </si>
-  <si>
-    <t>Real Newman output saved</t>
-  </si>
-  <si>
-    <t>TC-UI-ADM-001</t>
-  </si>
-  <si>
-    <t>SCN-GOV-004</t>
-  </si>
-  <si>
-    <t>Admin Users</t>
-  </si>
-  <si>
-    <t>Admin UI</t>
-  </si>
-  <si>
-    <t>Create a new admin user with valid group assignment</t>
-  </si>
-  <si>
-    <t>Hoang Van Thien</t>
-  </si>
-  <si>
-    <t>System creates the new admin account successfully; success toast appears; the new account is visible in the admin user list.</t>
-  </si>
-  <si>
     <t>TC-UI-ADM-002</t>
   </si>
   <si>
@@ -386,16 +361,16 @@
     <t>User is redirected to the admin area dashboard; authenticated session is established; no validation error is shown.</t>
   </si>
   <si>
-    <t>Reached the admin dashboard after valid login with admin@osms.local</t>
-  </si>
-  <si>
-    <t>evidence/ui/automation/20260405_115322_TC-UI-AUTH-001-success.png</t>
-  </si>
-  <si>
-    <t>results/automation-ui/ui-tests.trx</t>
-  </si>
-  <si>
-    <t>Real screenshot and TRX available</t>
+    <t>Valid admin login reached the admin dashboard successfully in the focused Selenium rerun.</t>
+  </si>
+  <si>
+    <t>evidence/ui/automation/20260406_053930_TC-UI-AUTH-001-success.png</t>
+  </si>
+  <si>
+    <t>results/automation-ui/auth-permission-rerun.trx</t>
+  </si>
+  <si>
+    <t>Focused UI reruns on 2026-04-06 confirmed login smoke still passes.</t>
   </si>
   <si>
     <t>TC-UI-AUTH-002</t>
@@ -425,22 +400,13 @@
     <t>System redirects the user to the Access Denied page or shows an equivalent permission denial response.</t>
   </si>
   <si>
-    <t>Selenium timeout while waiting for an access-denied state; screenshot shows sales@osms.local on the dashboard; product defect not confirmed</t>
-  </si>
-  <si>
-    <t>Automation Script Failure</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>evidence/ui/automation/20260405_115343_TC-UI-AUTH-003-failure.png</t>
-  </si>
-  <si>
-    <t>N/A - product defect not confirmed</t>
-  </si>
-  <si>
-    <t>Requires manual confirmation before defect logging</t>
+    <t>Direct navigation to /Admin/Purchases with sales@osms.local was rejected and redirected back to the dashboard instead of opening the Purchases module.</t>
+  </si>
+  <si>
+    <t>evidence/ui/automation/20260406_054245_TC-UI-AUTH-003-access-denied.png</t>
+  </si>
+  <si>
+    <t>Confirmed denial behavior from real rerun and server log shows GET /Admin/Purchases returned 302.</t>
   </si>
   <si>
     <t>TC-UI-AUTH-004</t>
@@ -452,6 +418,30 @@
     <t>Warehouse account is denied access to Invoices module</t>
   </si>
   <si>
+    <t>TC-UI-AUTH-005</t>
+  </si>
+  <si>
+    <t>SCN-AUTH-003</t>
+  </si>
+  <si>
+    <t>Inactive admin account is blocked from logging in</t>
+  </si>
+  <si>
+    <t>User remains on the login page; an inactive-account error message is shown; no authenticated admin session is created.</t>
+  </si>
+  <si>
+    <t>TC-UI-AUTH-006</t>
+  </si>
+  <si>
+    <t>SCN-GOV-003</t>
+  </si>
+  <si>
+    <t>Full admin account can open core management modules without access-denied responses</t>
+  </si>
+  <si>
+    <t>Each core management page opens successfully for the admin account; no access-denied page or equivalent permission error is shown.</t>
+  </si>
+  <si>
     <t>TC-UI-CUS-001</t>
   </si>
   <si>
@@ -533,10 +523,16 @@
     <t>Preview page opens successfully; total rows, valid rows, invalid rows, and row-level errors are displayed.</t>
   </si>
   <si>
-    <t>Selenium timeout before preview interaction completed; screenshot shows workbook already selected on the import page; product defect not confirmed</t>
-  </si>
-  <si>
-    <t>evidence/ui/automation/20260405_115405_TC-UI-IMP-002-failure.png</t>
+    <t>The mixed-validation workbook uploaded successfully and the preview page displayed 6 total rows, 1 valid row, and 5 invalid rows.</t>
+  </si>
+  <si>
+    <t>evidence/ui/automation/20260406_054115_TC-UI-IMP-002-preview.png</t>
+  </si>
+  <si>
+    <t>results/automation-ui/import-preview-rerun.trx</t>
+  </si>
+  <si>
+    <t>Previously blocked by a broad submit locator; focused rerun passed after locator fix.</t>
   </si>
   <si>
     <t>TC-UI-IMP-003</t>
@@ -575,7 +571,22 @@
     <t>Invoice is created successfully; details page is shown; invoice status is Unpaid; stock is reduced by the sold quantity.</t>
   </si>
   <si>
-    <t>Priority evidence still missing</t>
+    <t>Submitting a valid walk-in invoice returned to the Create page with the toast message Failed to create invoice. Please check data and try again. Server log confirms InvalidOperationException caused by a user-initiated transaction with MySqlRetryingExecutionStrategy in InvoicesController.Create line 145.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>evidence/ui/automation/20260406_053902_TC-UI-INV-001-failure.png</t>
+  </si>
+  <si>
+    <t>results/automation-ui/invoice-rerun.trx</t>
+  </si>
+  <si>
+    <t>BUG-20260406-001</t>
+  </si>
+  <si>
+    <t>Confirmed product defect with UI screenshot and server log excerpt evidence.</t>
   </si>
   <si>
     <t>TC-UI-INV-002</t>
@@ -626,6 +637,18 @@
     <t>Invoice status becomes Cancelled; stock increases by the cancelled quantity; a stock movement entry is recorded.</t>
   </si>
   <si>
+    <t>TC-UI-INV-006</t>
+  </si>
+  <si>
+    <t>SCN-INV-003</t>
+  </si>
+  <si>
+    <t>Invoice creation ignores a tampered client-posted unit price and uses the server-side sale price</t>
+  </si>
+  <si>
+    <t>The created invoice uses the server-side product SalePrice from the database, not the tampered client-posted UnitPrice; totals and line values reflect the real server-side price.</t>
+  </si>
+  <si>
     <t>TC-UI-PRD-001</t>
   </si>
   <si>
@@ -728,6 +751,18 @@
     <t>Displayed products match the selected price range and the listing order changes according to the selected sort option.</t>
   </si>
   <si>
+    <t>TC-UI-PUB-003</t>
+  </si>
+  <si>
+    <t>SCN-PUB-003</t>
+  </si>
+  <si>
+    <t>Public product details page shows the selected product information correctly</t>
+  </si>
+  <si>
+    <t>The details page opens for the selected product; the product name, category, brand, price, and navigation breadcrumb are displayed correctly.</t>
+  </si>
+  <si>
     <t>TC-UI-PUR-001</t>
   </si>
   <si>
@@ -743,6 +778,18 @@
     <t>Purchase is created successfully; details page is shown; generated purchase number is visible; status is Draft.</t>
   </si>
   <si>
+    <t>A valid draft purchase was created successfully and redirected to the purchase details page.</t>
+  </si>
+  <si>
+    <t>evidence/ui/automation/20260406_054004_TC-UI-PUR-001-draft-created.png</t>
+  </si>
+  <si>
+    <t>results/automation-ui/purchase-rerun.trx</t>
+  </si>
+  <si>
+    <t>Focused rerun passed after permission-aligned environment and stable form submit locator.</t>
+  </si>
+  <si>
     <t>TC-UI-PUR-002</t>
   </si>
   <si>
@@ -804,6 +851,12 @@
   </si>
   <si>
     <t>Purchase number, supplier, items, quantities, and totals are displayed correctly on the details screen.</t>
+  </si>
+  <si>
+    <t>The purchase details page showed the generated purchase number, supplier, line item, quantity, and totals correctly for the newly created draft purchase.</t>
+  </si>
+  <si>
+    <t>Validated by the same rerun that created the draft purchase because the assertions were executed on the details page.</t>
   </si>
   <si>
     <t>TC-UI-REP-001</t>
@@ -888,7 +941,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -896,16 +949,317 @@
       <family val="2"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF006100"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF9C0006"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF9C5700"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -913,16 +1267,205 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1253,29 +1796,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4F8631D-F62B-4867-9DD3-95C1FD44903C}">
-  <dimension ref="A1:R60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DAF756A-9758-43EB-8FB0-C231FFF72A80}">
+  <dimension ref="A1:R64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="174.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="129.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="64.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="44.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1335,7 +1858,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -1374,27 +1897,27 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -1406,7 +1929,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
         <v>23</v>
@@ -1418,7 +1941,7 @@
         <v>200</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
@@ -1430,27 +1953,27 @@
         <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -1462,7 +1985,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -1474,7 +1997,7 @@
         <v>200</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
@@ -1486,27 +2009,27 @@
         <v>27</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -1518,7 +2041,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
@@ -1530,7 +2053,7 @@
         <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
         <v>26</v>
@@ -1542,27 +2065,27 @@
         <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -1574,7 +2097,7 @@
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -1586,7 +2109,7 @@
         <v>200</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
         <v>26</v>
@@ -1598,30 +2121,30 @@
         <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1630,7 +2153,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -1642,7 +2165,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s">
         <v>26</v>
@@ -1654,30 +2177,30 @@
         <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1686,7 +2209,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -1698,7 +2221,7 @@
         <v>400</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
         <v>26</v>
@@ -1710,30 +2233,30 @@
         <v>27</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R8" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1742,7 +2265,7 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -1754,7 +2277,7 @@
         <v>400</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
         <v>26</v>
@@ -1766,30 +2289,30 @@
         <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R9" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
@@ -1798,7 +2321,7 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -1810,7 +2333,7 @@
         <v>400</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
         <v>26</v>
@@ -1822,30 +2345,30 @@
         <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
@@ -1854,7 +2377,7 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
@@ -1866,7 +2389,7 @@
         <v>400</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" t="s">
         <v>26</v>
@@ -1878,30 +2401,30 @@
         <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -1910,7 +2433,7 @@
         <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
@@ -1922,7 +2445,7 @@
         <v>400</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K12" t="s">
         <v>26</v>
@@ -1934,30 +2457,30 @@
         <v>27</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R12" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
@@ -1966,7 +2489,7 @@
         <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
@@ -1978,7 +2501,7 @@
         <v>400</v>
       </c>
       <c r="J13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K13" t="s">
         <v>26</v>
@@ -1990,30 +2513,30 @@
         <v>27</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R13" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
@@ -2022,7 +2545,7 @@
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
@@ -2034,7 +2557,7 @@
         <v>400</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
@@ -2046,30 +2569,30 @@
         <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R14" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
@@ -2078,7 +2601,7 @@
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
         <v>23</v>
@@ -2090,7 +2613,7 @@
         <v>200</v>
       </c>
       <c r="J15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K15" t="s">
         <v>26</v>
@@ -2102,24 +2625,24 @@
         <v>27</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R15" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
@@ -2158,24 +2681,24 @@
         <v>27</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R16" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
@@ -2214,24 +2737,24 @@
         <v>27</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R17" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
@@ -2270,27 +2793,27 @@
         <v>27</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R18" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
         <v>80</v>
@@ -2302,7 +2825,7 @@
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
@@ -2314,7 +2837,7 @@
         <v>200</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
@@ -2326,763 +2849,763 @@
         <v>27</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R19" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
         <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I20">
         <v>200</v>
       </c>
       <c r="J20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>30</v>
+      </c>
+      <c r="R20" t="s">
         <v>93</v>
-      </c>
-      <c r="K20" t="s">
-        <v>94</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
-      </c>
-      <c r="M20" t="s">
-        <v>95</v>
-      </c>
-      <c r="N20" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" t="s">
-        <v>97</v>
-      </c>
-      <c r="P20" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>28</v>
-      </c>
-      <c r="R20" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
         <v>99</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s">
-        <v>104</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L21" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M21" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O21" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P21" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R21" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H22" t="s">
         <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N22" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O22" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R22" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
         <v>110</v>
       </c>
-      <c r="C23" t="s">
+      <c r="G23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" t="s">
         <v>111</v>
       </c>
-      <c r="D23" t="s">
+      <c r="J23" t="s">
         <v>112</v>
       </c>
-      <c r="E23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="K23" t="s">
         <v>113</v>
       </c>
-      <c r="G23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" t="s">
         <v>114</v>
       </c>
-      <c r="J23" t="s">
+      <c r="O23" t="s">
         <v>115</v>
       </c>
-      <c r="K23" t="s">
+      <c r="P23" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>30</v>
+      </c>
+      <c r="R23" t="s">
         <v>116</v>
-      </c>
-      <c r="L23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M23" t="s">
-        <v>95</v>
-      </c>
-      <c r="N23" t="s">
-        <v>117</v>
-      </c>
-      <c r="O23" t="s">
-        <v>118</v>
-      </c>
-      <c r="P23" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>28</v>
-      </c>
-      <c r="R23" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" t="s">
         <v>120</v>
       </c>
-      <c r="C24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" t="s">
-        <v>114</v>
-      </c>
-      <c r="J24" t="s">
-        <v>123</v>
-      </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M24" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O24" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P24" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R24" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
         <v>124</v>
       </c>
-      <c r="C25" t="s">
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" t="s">
+        <v>111</v>
+      </c>
+      <c r="J25" t="s">
         <v>125</v>
       </c>
-      <c r="D25" t="s">
+      <c r="K25" t="s">
         <v>126</v>
       </c>
-      <c r="E25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" t="s">
         <v>127</v>
       </c>
-      <c r="G25" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" t="s">
-        <v>114</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="O25" t="s">
+        <v>115</v>
+      </c>
+      <c r="P25" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>30</v>
+      </c>
+      <c r="R25" t="s">
         <v>128</v>
-      </c>
-      <c r="K25" t="s">
-        <v>129</v>
-      </c>
-      <c r="L25" t="s">
-        <v>130</v>
-      </c>
-      <c r="M25" t="s">
-        <v>131</v>
-      </c>
-      <c r="N25" t="s">
-        <v>132</v>
-      </c>
-      <c r="O25" t="s">
-        <v>118</v>
-      </c>
-      <c r="P25" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>133</v>
-      </c>
-      <c r="R25" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J26" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L26" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M26" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O26" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P26" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R26" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L27" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O27" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P27" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R27" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
       </c>
       <c r="J28" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M28" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O28" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R28" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L29" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N29" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O29" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P29" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R29" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K30" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M30" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O30" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P30" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R30" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
+        <v>144</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>152</v>
+      </c>
+      <c r="K31" t="s">
+        <v>101</v>
+      </c>
+      <c r="L31" t="s">
+        <v>102</v>
+      </c>
+      <c r="M31" t="s">
+        <v>102</v>
+      </c>
+      <c r="N31" t="s">
+        <v>101</v>
+      </c>
+      <c r="O31" t="s">
+        <v>101</v>
+      </c>
+      <c r="P31" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>30</v>
+      </c>
+      <c r="R31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>155</v>
+      </c>
+      <c r="E32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" t="s">
         <v>156</v>
       </c>
-      <c r="C31" t="s">
+      <c r="G32" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" t="s">
         <v>157</v>
       </c>
-      <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" t="s">
-        <v>102</v>
-      </c>
-      <c r="F31" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" t="s">
-        <v>114</v>
-      </c>
-      <c r="J31" t="s">
-        <v>161</v>
-      </c>
-      <c r="K31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" t="s">
-        <v>27</v>
-      </c>
-      <c r="N31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" t="s">
-        <v>26</v>
-      </c>
-      <c r="P31" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B32" t="s">
-        <v>162</v>
-      </c>
-      <c r="C32" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" t="s">
-        <v>160</v>
-      </c>
-      <c r="H32" t="s">
-        <v>114</v>
-      </c>
-      <c r="J32" t="s">
-        <v>164</v>
-      </c>
       <c r="K32" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="L32" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="M32" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="N32" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="O32" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q32" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="R32" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" t="s">
+        <v>111</v>
+      </c>
+      <c r="J33" t="s">
+        <v>163</v>
+      </c>
+      <c r="K33" t="s">
+        <v>101</v>
+      </c>
+      <c r="L33" t="s">
+        <v>102</v>
+      </c>
+      <c r="M33" t="s">
+        <v>102</v>
+      </c>
+      <c r="N33" t="s">
+        <v>101</v>
+      </c>
+      <c r="O33" t="s">
+        <v>101</v>
+      </c>
+      <c r="P33" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>30</v>
+      </c>
+      <c r="R33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B34" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>165</v>
+      </c>
+      <c r="G34" t="s">
+        <v>162</v>
+      </c>
+      <c r="H34" t="s">
+        <v>111</v>
+      </c>
+      <c r="J34" t="s">
+        <v>166</v>
+      </c>
+      <c r="K34" t="s">
         <v>167</v>
-      </c>
-      <c r="C33" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" t="s">
-        <v>169</v>
-      </c>
-      <c r="G33" t="s">
-        <v>160</v>
-      </c>
-      <c r="H33" t="s">
-        <v>114</v>
-      </c>
-      <c r="J33" t="s">
-        <v>170</v>
-      </c>
-      <c r="K33" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N33" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" t="s">
-        <v>26</v>
-      </c>
-      <c r="P33" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>28</v>
-      </c>
-      <c r="R33" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" t="s">
-        <v>158</v>
-      </c>
-      <c r="E34" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" t="s">
-        <v>172</v>
-      </c>
-      <c r="G34" t="s">
-        <v>160</v>
-      </c>
-      <c r="H34" t="s">
-        <v>114</v>
-      </c>
-      <c r="J34" t="s">
-        <v>173</v>
-      </c>
-      <c r="K34" t="s">
-        <v>26</v>
       </c>
       <c r="L34" t="s">
         <v>27</v>
@@ -3091,322 +3614,322 @@
         <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="O34" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="P34" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R34" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>46117</v>
-      </c>
       <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" t="s">
+        <v>162</v>
+      </c>
+      <c r="H35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J35" t="s">
         <v>174</v>
       </c>
-      <c r="C35" t="s">
-        <v>175</v>
-      </c>
-      <c r="D35" t="s">
-        <v>176</v>
-      </c>
-      <c r="E35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G35" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" t="s">
-        <v>114</v>
-      </c>
-      <c r="J35" t="s">
-        <v>178</v>
-      </c>
       <c r="K35" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M35" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N35" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O35" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P35" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R35" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" t="s">
+        <v>111</v>
+      </c>
+      <c r="J36" t="s">
+        <v>177</v>
+      </c>
+      <c r="K36" t="s">
+        <v>101</v>
+      </c>
+      <c r="L36" t="s">
+        <v>102</v>
+      </c>
+      <c r="M36" t="s">
+        <v>102</v>
+      </c>
+      <c r="N36" t="s">
+        <v>101</v>
+      </c>
+      <c r="O36" t="s">
+        <v>101</v>
+      </c>
+      <c r="P36" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>30</v>
+      </c>
+      <c r="R36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" t="s">
         <v>180</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" t="s">
         <v>181</v>
       </c>
-      <c r="D36" t="s">
-        <v>176</v>
-      </c>
-      <c r="E36" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H37" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" t="s">
         <v>182</v>
       </c>
-      <c r="G36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K37" t="s">
         <v>183</v>
       </c>
-      <c r="K36" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" t="s">
-        <v>27</v>
-      </c>
-      <c r="M36" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" t="s">
-        <v>26</v>
-      </c>
-      <c r="P36" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>28</v>
-      </c>
-      <c r="R36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
+      <c r="L37" t="s">
         <v>184</v>
       </c>
-      <c r="C37" t="s">
+      <c r="M37" t="s">
+        <v>184</v>
+      </c>
+      <c r="N37" t="s">
         <v>185</v>
       </c>
-      <c r="D37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="O37" t="s">
         <v>186</v>
       </c>
-      <c r="G37" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" t="s">
-        <v>114</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="P37" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q37" t="s">
         <v>187</v>
       </c>
-      <c r="K37" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" t="s">
-        <v>27</v>
-      </c>
-      <c r="M37" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" t="s">
-        <v>26</v>
-      </c>
-      <c r="P37" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>28</v>
-      </c>
       <c r="R37" t="s">
-        <v>26</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H38" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M38" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H39" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O39" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P39" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R39" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D40" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
         <v>199</v>
       </c>
       <c r="G40" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J40" t="s">
         <v>200</v>
       </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M40" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O40" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P40" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R40" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -3417,46 +3940,46 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s">
         <v>203</v>
       </c>
       <c r="G41" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H41" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J41" t="s">
         <v>204</v>
       </c>
       <c r="K41" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M41" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O41" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P41" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R41" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -3467,46 +3990,46 @@
         <v>206</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
         <v>207</v>
       </c>
       <c r="G42" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J42" t="s">
         <v>208</v>
       </c>
       <c r="K42" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M42" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O42" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P42" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R42" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
@@ -3514,352 +4037,349 @@
         <v>209</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H43" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J43" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K43" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L43" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M43" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N43" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O43" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R43" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J44" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K44" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N44" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O44" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P44" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R44" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K45" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O45" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P45" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R45" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" t="s">
         <v>223</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
+        <v>162</v>
+      </c>
+      <c r="H46" t="s">
+        <v>111</v>
+      </c>
+      <c r="J46" t="s">
         <v>224</v>
       </c>
-      <c r="G46" t="s">
-        <v>160</v>
-      </c>
-      <c r="H46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" t="s">
-        <v>225</v>
-      </c>
       <c r="K46" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L46" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M46" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N46" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O46" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P46" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q46" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R46" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" t="s">
         <v>226</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s">
         <v>227</v>
       </c>
-      <c r="D47" t="s">
-        <v>222</v>
-      </c>
-      <c r="E47" t="s">
-        <v>223</v>
-      </c>
-      <c r="F47" t="s">
-        <v>228</v>
-      </c>
       <c r="G47" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="H47" t="s">
         <v>24</v>
       </c>
       <c r="J47" t="s">
+        <v>228</v>
+      </c>
+      <c r="K47" t="s">
+        <v>101</v>
+      </c>
+      <c r="L47" t="s">
+        <v>102</v>
+      </c>
+      <c r="M47" t="s">
+        <v>102</v>
+      </c>
+      <c r="N47" t="s">
+        <v>101</v>
+      </c>
+      <c r="O47" t="s">
+        <v>101</v>
+      </c>
+      <c r="P47" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>30</v>
+      </c>
+      <c r="R47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
         <v>229</v>
       </c>
-      <c r="K47" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" t="s">
-        <v>27</v>
-      </c>
-      <c r="M47" t="s">
-        <v>27</v>
-      </c>
-      <c r="N47" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" t="s">
-        <v>26</v>
-      </c>
-      <c r="P47" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>28</v>
-      </c>
-      <c r="R47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>230</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
         <v>231</v>
       </c>
-      <c r="D48" t="s">
+      <c r="G48" t="s">
+        <v>162</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
         <v>232</v>
       </c>
-      <c r="E48" t="s">
-        <v>102</v>
-      </c>
-      <c r="F48" t="s">
-        <v>233</v>
-      </c>
-      <c r="G48" t="s">
-        <v>142</v>
-      </c>
-      <c r="H48" t="s">
-        <v>114</v>
-      </c>
-      <c r="J48" t="s">
-        <v>234</v>
-      </c>
       <c r="K48" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N48" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O48" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P48" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q48" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R48" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" t="s">
         <v>235</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>236</v>
-      </c>
-      <c r="D49" t="s">
-        <v>232</v>
-      </c>
-      <c r="E49" t="s">
-        <v>102</v>
       </c>
       <c r="F49" t="s">
         <v>237</v>
       </c>
       <c r="G49" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H49" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="J49" t="s">
         <v>238</v>
       </c>
       <c r="K49" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L49" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M49" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N49" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O49" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P49" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q49" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R49" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -3867,128 +4387,131 @@
         <v>239</v>
       </c>
       <c r="C50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" t="s">
         <v>236</v>
       </c>
-      <c r="D50" t="s">
-        <v>232</v>
-      </c>
-      <c r="E50" t="s">
-        <v>102</v>
-      </c>
       <c r="F50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G50" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H50" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="J50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K50" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L50" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N50" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O50" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P50" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q50" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R50" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="F51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G51" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H51" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K51" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L51" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M51" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N51" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O51" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P51" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R51" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>46118</v>
+      </c>
       <c r="B52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G52" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H52" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J52" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K52" t="s">
-        <v>26</v>
+        <v>252</v>
       </c>
       <c r="L52" t="s">
         <v>27</v>
@@ -3997,301 +4520,301 @@
         <v>27</v>
       </c>
       <c r="N52" t="s">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="O52" t="s">
-        <v>26</v>
+        <v>254</v>
       </c>
       <c r="P52" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R52" t="s">
-        <v>26</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F53" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="G53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J53" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M53" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N53" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O53" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P53" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q53" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R53" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>46117</v>
-      </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C54" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D54" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F54" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G54" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J54" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N54" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O54" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P54" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q54" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R54" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C55" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D55" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E55" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F55" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G55" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="H55" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J55" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="K55" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L55" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M55" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N55" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O55" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P55" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q55" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R55" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D56" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F56" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G56" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="H56" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J56" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K56" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M56" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N56" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O56" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P56" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q56" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R56" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D57" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F57" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G57" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="J57" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K57" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O57" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P57" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R57" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>46118</v>
+      </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D58" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E58" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F58" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G58" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H58" t="s">
         <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="L58" t="s">
         <v>27</v>
@@ -4300,122 +4823,322 @@
         <v>27</v>
       </c>
       <c r="N58" t="s">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="O58" t="s">
-        <v>26</v>
+        <v>254</v>
       </c>
       <c r="P58" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q58" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R58" t="s">
-        <v>26</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C59" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D59" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F59" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G59" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H59" t="s">
         <v>24</v>
       </c>
       <c r="J59" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L59" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M59" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N59" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O59" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P59" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q59" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R59" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D60" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F60" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G60" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H60" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="J60" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K60" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="L60" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="M60" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="N60" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O60" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="P60" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="Q60" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R60" t="s">
-        <v>26</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>288</v>
+      </c>
+      <c r="C61" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" t="s">
+        <v>290</v>
+      </c>
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" t="s">
+        <v>291</v>
+      </c>
+      <c r="G61" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" t="s">
+        <v>292</v>
+      </c>
+      <c r="K61" t="s">
+        <v>101</v>
+      </c>
+      <c r="L61" t="s">
+        <v>102</v>
+      </c>
+      <c r="M61" t="s">
+        <v>102</v>
+      </c>
+      <c r="N61" t="s">
+        <v>101</v>
+      </c>
+      <c r="O61" t="s">
+        <v>101</v>
+      </c>
+      <c r="P61" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>30</v>
+      </c>
+      <c r="R61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>293</v>
+      </c>
+      <c r="C62" t="s">
+        <v>294</v>
+      </c>
+      <c r="D62" t="s">
+        <v>290</v>
+      </c>
+      <c r="E62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" t="s">
+        <v>144</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" t="s">
+        <v>296</v>
+      </c>
+      <c r="K62" t="s">
+        <v>101</v>
+      </c>
+      <c r="L62" t="s">
+        <v>102</v>
+      </c>
+      <c r="M62" t="s">
+        <v>102</v>
+      </c>
+      <c r="N62" t="s">
+        <v>101</v>
+      </c>
+      <c r="O62" t="s">
+        <v>101</v>
+      </c>
+      <c r="P62" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>30</v>
+      </c>
+      <c r="R62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>297</v>
+      </c>
+      <c r="C63" t="s">
+        <v>294</v>
+      </c>
+      <c r="D63" t="s">
+        <v>290</v>
+      </c>
+      <c r="E63" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" t="s">
+        <v>298</v>
+      </c>
+      <c r="G63" t="s">
+        <v>162</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" t="s">
+        <v>299</v>
+      </c>
+      <c r="K63" t="s">
+        <v>101</v>
+      </c>
+      <c r="L63" t="s">
+        <v>102</v>
+      </c>
+      <c r="M63" t="s">
+        <v>102</v>
+      </c>
+      <c r="N63" t="s">
+        <v>101</v>
+      </c>
+      <c r="O63" t="s">
+        <v>101</v>
+      </c>
+      <c r="P63" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>30</v>
+      </c>
+      <c r="R63" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>300</v>
+      </c>
+      <c r="C64" t="s">
+        <v>301</v>
+      </c>
+      <c r="D64" t="s">
+        <v>302</v>
+      </c>
+      <c r="E64" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" t="s">
+        <v>303</v>
+      </c>
+      <c r="G64" t="s">
+        <v>144</v>
+      </c>
+      <c r="H64" t="s">
+        <v>90</v>
+      </c>
+      <c r="J64" t="s">
+        <v>304</v>
+      </c>
+      <c r="K64" t="s">
+        <v>101</v>
+      </c>
+      <c r="L64" t="s">
+        <v>102</v>
+      </c>
+      <c r="M64" t="s">
+        <v>102</v>
+      </c>
+      <c r="N64" t="s">
+        <v>101</v>
+      </c>
+      <c r="O64" t="s">
+        <v>101</v>
+      </c>
+      <c r="P64" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>30</v>
+      </c>
+      <c r="R64" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>